--- a/04_DESIGN_TABLES/DesignTable_5652.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5652.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,6 +524,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1139,24 +1144,68 @@
           <t>5652-02-02-02-02-FG</t>
         </is>
       </c>
+      <c r="B11" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.405</v>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
           <t>5652-02-02-02-02-FG</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>1/8-27 (A (1) NPTF) x 1/8-27 (A (2) NPTF) x 1/8-27 (A (3) NPTF) x 1/8-27 (A (4) NPTF)</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5652-02-02-02-02 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5652-02-02-02-02 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N1_1@DRIVE: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-02-02-02-02-FG col "N LGTH" = "0.66" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 431.4, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N1_2@DRIVE: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-02-02-02-02-FG col "N LGTH" = "0.66" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 431.4, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N1_3@DRIVE: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-02-02-02-02-FG col "N LGTH" = "0.66" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 431.4, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N1_4@DRIVE: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-02-02-02-02-FG col "N LGTH" = "0.66" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 431.4, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); W@HEX: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-02-02-02-02-FG col "Y FLATS" = "0.562" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 431.4, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); TAPDRILL1@BORE: end library: tap drill of the -02 female NPTF port = 0.33 (gen_straight2 FPT[2] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-02-02) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; TAPDRILL2@BORE: end library: tap drill of the -02 female NPTF port = 0.33 (gen_straight2 FPT[2] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-02-02) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; TAPDRILL3@BORE: end library: tap drill of the -02 female NPTF port = 0.33 (gen_straight2 FPT[2] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-02-02) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; TAPDRILL4@BORE: end library: tap drill of the -02 female NPTF port = 0.33 (gen_straight2 FPT[2] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-02-02) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; THDMAJ_A1@DRIVE: end library: pipe OD of the -02 NPTF thread = 0.405 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[2], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -02 NPTF thread = 0.405 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[2], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A3@DRIVE: end library: pipe OD of the -02 NPTF thread = 0.405 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[2], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A4@DRIVE: end library: pipe OD of the -02 NPTF thread = 0.405 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[2], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes (format of the table's other rows); = OMi WebsitePartsInfo2026 Items Side n Thread</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5652-02-02-02-02 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5652-02-02-02-02 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5652-02-02-02-02 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate)</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1167,6 +1216,11 @@
       <c r="U11" t="inlineStr">
         <is>
           <t>5652-02-02-02-02-FG</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1176,24 +1230,68 @@
           <t>5652-04-04-04-04-FG</t>
         </is>
       </c>
+      <c r="B12" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.54</v>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
           <t>5652-04-04-04-04-FG</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>1/4-18 (A (1) NPTF) x 1/4-18 (A (2) NPTF) x 1/4-18 (A (3) NPTF) x 1/4-18 (A (4) NPTF)</t>
+        </is>
+      </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5652-04-04-04-04 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5652-04-04-04-04 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N1_1@DRIVE: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-04-04-04-04-FG col "N LGTH" = "0.88" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 441.5, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N1_2@DRIVE: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-04-04-04-04-FG col "N LGTH" = "0.88" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 441.5, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N1_3@DRIVE: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-04-04-04-04-FG col "N LGTH" = "0.88" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 441.5, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N1_4@DRIVE: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-04-04-04-04-FG col "N LGTH" = "0.88" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 441.5, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); W@HEX: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-04-04-04-04-FG col "Y FLATS" = "0.750" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 441.5, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); TAPDRILL1@BORE: end library: tap drill of the -04 female NPTF port = 0.43 (gen_straight2 FPT[4] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-03-04) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; TAPDRILL2@BORE: end library: tap drill of the -04 female NPTF port = 0.43 (gen_straight2 FPT[4] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-03-04) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; TAPDRILL3@BORE: end library: tap drill of the -04 female NPTF port = 0.43 (gen_straight2 FPT[4] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-03-04) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; TAPDRILL4@BORE: end library: tap drill of the -04 female NPTF port = 0.43 (gen_straight2 FPT[4] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-03-04) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; THDMAJ_A1@DRIVE: end library: pipe OD of the -04 NPTF thread = 0.54 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[4], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -04 NPTF thread = 0.54 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[4], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A3@DRIVE: end library: pipe OD of the -04 NPTF thread = 0.54 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[4], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A4@DRIVE: end library: pipe OD of the -04 NPTF thread = 0.54 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[4], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes (format of the table's other rows); = OMi WebsitePartsInfo2026 Items Side n Thread</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5652-04-04-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5652-04-04-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5652-04-04-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate)</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1204,6 +1302,11 @@
       <c r="U12" t="inlineStr">
         <is>
           <t>5652-04-04-04-04-FG</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1213,24 +1316,68 @@
           <t>5652-06-06-06-06-FG</t>
         </is>
       </c>
+      <c r="B13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.675</v>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
           <t>5652-06-06-06-06-FG</t>
         </is>
       </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>3/8-18 (A (1) NPTF) x 3/8-18 (A (2) NPTF) x 3/8-18 (A (3) NPTF) x 3/8-18 (A (4) NPTF)</t>
+        </is>
+      </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5652-06-06-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5652-06-06-06-06 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N1_1@DRIVE: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-06-06-06-06-FG col "N LGTH" = "1.020" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 451.6, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N1_2@DRIVE: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-06-06-06-06-FG col "N LGTH" = "1.020" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 451.6, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N1_3@DRIVE: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-06-06-06-06-FG col "N LGTH" = "1.020" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 451.6, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N1_4@DRIVE: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-06-06-06-06-FG col "N LGTH" = "1.020" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 451.6, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); W@HEX: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-06-06-06-06-FG col "Y FLATS" = "0.875" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 451.6, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); TAPDRILL1@BORE: end library: tap drill of the -06 female NPTF port = 0.57 (gen_straight2 FPT[6] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-04-06) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; TAPDRILL2@BORE: end library: tap drill of the -06 female NPTF port = 0.57 (gen_straight2 FPT[6] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-04-06) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; TAPDRILL3@BORE: end library: tap drill of the -06 female NPTF port = 0.57 (gen_straight2 FPT[6] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-04-06) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; TAPDRILL4@BORE: end library: tap drill of the -06 female NPTF port = 0.57 (gen_straight2 FPT[6] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-04-06) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; THDMAJ_A1@DRIVE: end library: pipe OD of the -06 NPTF thread = 0.675 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[6], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -06 NPTF thread = 0.675 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[6], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A3@DRIVE: end library: pipe OD of the -06 NPTF thread = 0.675 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[6], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A4@DRIVE: end library: pipe OD of the -06 NPTF thread = 0.675 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[6], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes (format of the table's other rows); = OMi WebsitePartsInfo2026 Items Side n Thread</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5652-06-06-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5652-06-06-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5652-06-06-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate)</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -1241,6 +1388,11 @@
       <c r="U13" t="inlineStr">
         <is>
           <t>5652-06-06-06-06-FG</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1287,24 +1439,68 @@
           <t>5652-12-12-12-12-FG</t>
         </is>
       </c>
+      <c r="B15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.05</v>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
           <t>5652-12-12-12-12-FG</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>3/4-14 (A (1) NPTF) x 3/4-14 (A (2) NPTF) x 3/4-14 (A (3) NPTF) x 3/4-14 (A (4) NPTF)</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5652-12-12-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5652-12-12-12-12 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N1_1@DRIVE: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-12-12-12-12-FG col "N LGTH" = "1.360" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 471.8, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N1_2@DRIVE: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-12-12-12-12-FG col "N LGTH" = "1.360" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 471.8, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N1_3@DRIVE: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-12-12-12-12-FG col "N LGTH" = "1.360" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 471.8, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N1_4@DRIVE: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-12-12-12-12-FG col "N LGTH" = "1.360" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 471.8, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); W@HEX: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-12-12-12-12-FG col "Y FLATS" = "1.312" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 471.8, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); TAPDRILL1@BORE: end library: tap drill of the -12 female NPTF port = 0.91 (gen_straight2 FPT[12] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-08-12) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; TAPDRILL2@BORE: end library: tap drill of the -12 female NPTF port = 0.91 (gen_straight2 FPT[12] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-08-12) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; TAPDRILL3@BORE: end library: tap drill of the -12 female NPTF port = 0.91 (gen_straight2 FPT[12] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-08-12) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; TAPDRILL4@BORE: end library: tap drill of the -12 female NPTF port = 0.91 (gen_straight2 FPT[12] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-08-12) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; THDMAJ_A1@DRIVE: end library: pipe OD of the -12 NPTF thread = 1.05 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[12], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -12 NPTF thread = 1.05 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[12], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A3@DRIVE: end library: pipe OD of the -12 NPTF thread = 1.05 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[12], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A4@DRIVE: end library: pipe OD of the -12 NPTF thread = 1.05 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[12], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes (format of the table's other rows); = OMi WebsitePartsInfo2026 Items Side n Thread</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5652-12-12-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5652-12-12-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5652-12-12-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate)</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -1315,6 +1511,11 @@
       <c r="U15" t="inlineStr">
         <is>
           <t>5652-12-12-12-12-FG</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1525,68 @@
           <t>5652-16-16-16-16-FG</t>
         </is>
       </c>
+      <c r="B16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.315</v>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
           <t>5652-16-16-16-16-FG</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>1-11 1/2 (A (1) NPTF) x 1-11 1/2 (A (2) NPTF) x 1-11 1/2 (A (3) NPTF) x 1-11 1/2 (A (4) NPTF)</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5652-16-16-16-16 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5652-16-16-16-16 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N1_1@DRIVE: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-16-16-16-16-FG col "N LGTH" = "1.62" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 481.8, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N1_2@DRIVE: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-16-16-16-16-FG col "N LGTH" = "1.62" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 481.8, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N1_3@DRIVE: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-16-16-16-16-FG col "N LGTH" = "1.62" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 481.8, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N1_4@DRIVE: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-16-16-16-16-FG col "N LGTH" = "1.62" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 481.8, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); W@HEX: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-16-16-16-16-FG col "Y FLATS" = "1.625" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 481.8, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); TAPDRILL1@BORE: end library: tap drill of the -16 female NPTF port = 1.14 (gen_straight2 FPT[16] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-12-16) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; TAPDRILL2@BORE: end library: tap drill of the -16 female NPTF port = 1.14 (gen_straight2 FPT[16] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-12-16) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; TAPDRILL3@BORE: end library: tap drill of the -16 female NPTF port = 1.14 (gen_straight2 FPT[16] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-12-16) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; TAPDRILL4@BORE: end library: tap drill of the -16 female NPTF port = 1.14 (gen_straight2 FPT[16] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-12-16) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; THDMAJ_A1@DRIVE: end library: pipe OD of the -16 NPTF thread = 1.315 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[16], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -16 NPTF thread = 1.315 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[16], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A3@DRIVE: end library: pipe OD of the -16 NPTF thread = 1.315 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[16], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A4@DRIVE: end library: pipe OD of the -16 NPTF thread = 1.315 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[16], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes (format of the table's other rows); = OMi WebsitePartsInfo2026 Items Side n Thread</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5652-16-16-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5652-16-16-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5652-16-16-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate)</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -1352,6 +1597,11 @@
       <c r="U16" t="inlineStr">
         <is>
           <t>5652-16-16-16-16-FG</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1361,24 +1611,68 @@
           <t>5652-20-20-20-20-FG</t>
         </is>
       </c>
+      <c r="B17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.66</v>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
           <t>5652-20-20-20-20-FG</t>
         </is>
       </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 (A (1) NPTF) x 1 1/4-11 1/2 (A (2) NPTF) x 1 1/4-11 1/2 (A (3) NPTF) x 1 1/4-11 1/2 (A (4) NPTF)</t>
+        </is>
+      </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5652-20-20-20-20 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5652-20-20-20-20 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N1_1@DRIVE: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-20-20-20-20-FG col "N LGTH" = "1.70" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 491.9, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N1_2@DRIVE: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-20-20-20-20-FG col "N LGTH" = "1.70" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 491.9, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N1_3@DRIVE: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-20-20-20-20-FG col "N LGTH" = "1.70" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 491.9, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); N1_4@DRIVE: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-20-20-20-20-FG col "N LGTH" = "1.70" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 491.9, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); W@HEX: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-20-20-20-20-FG col "Y FLATS" = "1.875" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 491.9, page verified True) [Brennan = yes 2026-10-18] (column pairing of the PIPE-TEES work group, checked on the pilot STEP of the series); TAPDRILL1@BORE: end library: tap drill of the -20 female NPTF port = 1.48 (gen_straight2 FPT[20] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-16-20) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; TAPDRILL2@BORE: end library: tap drill of the -20 female NPTF port = 1.48 (gen_straight2 FPT[20] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-16-20) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; TAPDRILL3@BORE: end library: tap drill of the -20 female NPTF port = 1.48 (gen_straight2 FPT[20] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-16-20) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; TAPDRILL4@BORE: end library: tap drill of the -20 female NPTF port = 1.48 (gen_straight2 FPT[20] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-16-20) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; THDMAJ_A1@DRIVE: end library: pipe OD of the -20 NPTF thread = 1.66 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[20], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -20 NPTF thread = 1.66 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[20], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A3@DRIVE: end library: pipe OD of the -20 NPTF thread = 1.66 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[20], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A4@DRIVE: end library: pipe OD of the -20 NPTF thread = 1.66 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[20], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes (format of the table's other rows); = OMi WebsitePartsInfo2026 Items Side n Thread</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5652-20-20-20-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5652-20-20-20-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5652-20-20-20-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate)</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -1389,6 +1683,11 @@
       <c r="U17" t="inlineStr">
         <is>
           <t>5652-20-20-20-20-FG</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_5652.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5652.xlsx
@@ -1402,24 +1402,68 @@
           <t>5652-08-08-08-08-FG</t>
         </is>
       </c>
+      <c r="B14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.84</v>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>5652-08-08-08-08-FG</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>1/2-14 (A (1) NPTF) x 1/2-14 (A (2) NPTF) x 1/2-14 (A (3) NPTF) x 1/2-14 (A (4) NPTF)</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5652-08-08-08-08 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-21] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5652-08-08-08-08 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-21 (batch 19 C, staged): Brennan allowed (user 2026-10-18 "yes use brennan but still differentiate"); Air-Way prints no value for this part number, OMi's website file gives no dimension; sizes from the Brennan TFA catalog, each checked on the part's OWN Brennan STEP (09_STEP_FILES/BRENNAN_5652-08-08-08-08-FG.stp, every value equal to the catalog within 0.005); end details from the end library: N1_1@DRIVE: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-08-08-08-08-FG col "N LGTH" = "1.23" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 461.7, page verified True) [Brennan = yes 2026-10-18] - female port 1: crossing to the port face; own STEP: all four port faces 1.23 (C_ownstep/measure/5652-08-08-08-08-FG.txt (pipetee.py)); N1_2@DRIVE: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-08-08-08-08-FG col "N LGTH" = "1.23" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 461.7, page verified True) [Brennan = yes 2026-10-18] - female port 2: crossing to the port face; own STEP: all four port faces 1.23 (C_ownstep/measure/5652-08-08-08-08-FG.txt (pipetee.py)); N1_3@DRIVE: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-08-08-08-08-FG col "N LGTH" = "1.23" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 461.7, page verified True) [Brennan = yes 2026-10-18] - female port 3: crossing to the port face; own STEP: all four port faces 1.23 (C_ownstep/measure/5652-08-08-08-08-FG.txt (pipetee.py)); N1_4@DRIVE: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-08-08-08-08-FG col "N LGTH" = "1.23" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 461.7, page verified True) [Brennan = yes 2026-10-18] - female port 4: crossing to the port face; own STEP: all four port faces 1.23 (C_ownstep/measure/5652-08-08-08-08-FG.txt (pipetee.py)); W@HEX: Brennan TFA catalog p.63 table TFA-p063-t03 "5652-FG FP-FP-FP-FP-CROSS" row 5652-08-08-08-08-FG col "Y FLATS" = "1.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 461.7, page verified True) [Brennan = yes 2026-10-18] - forged body flats; own STEP: A/F 1.062 on every leg (C_ownstep/measure/5652-08-08-08-08-FG.txt (pipetee.py)); TAPDRILL1@BORE: end library: tap drill of the -08 female NPTF port = 0.7 (gen_straight2 FPT[8] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-08-08) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library] (own STEP: Brennan port drill 0.718); TAPDRILL2@BORE: end library: tap drill of the -08 female NPTF port = 0.7 (gen_straight2 FPT[8] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-08-08) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library] (own STEP: Brennan port drill 0.718); TAPDRILL3@BORE: end library: tap drill of the -08 female NPTF port = 0.7 (gen_straight2 FPT[8] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-08-08) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library] (own STEP: Brennan port drill 0.718); TAPDRILL4@BORE: end library: tap drill of the -08 female NPTF port = 0.7 (gen_straight2 FPT[8] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-08-08) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library] (own STEP: Brennan port drill 0.718); THDMAJ_A1@DRIVE: end library: pipe OD of the -08 NPTF thread = 0.84 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[8], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -08 NPTF thread = 0.84 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[8], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A3@DRIVE: end library: pipe OD of the -08 NPTF thread = 0.84 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[8], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A4@DRIVE: end library: pipe OD of the -08 NPTF thread = 0.84 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[8], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5652-08-08-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5652-08-08-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-21 batch 19 C (staged, not shipped): filled from the Brennan TFA catalog, checked on the own STEP (tools/_out/batch19_20261021/C_ownstep/measure); marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate). Cross-check only: Air-Way 5652-8-8-8-8 (plain): N 1.23 x4 W 1.13 TAPDRILL 0.70 (legs agree; flats differ: forged 1.062)</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -1430,6 +1474,11 @@
       <c r="U14" t="inlineStr">
         <is>
           <t>5652-08-08-08-08-FG</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
